--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Purén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carahue</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:20</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -826,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9208</v>
+        <v>9207</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
+    <t xml:space="preserve">Lumaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carahue</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:11</t>
+    <t xml:space="preserve">2026-09-23 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -826,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9208</v>
+        <v>9207</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:40</t>
+    <t xml:space="preserve">2026-10-02 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:07</t>
+    <t xml:space="preserve">2026-10-05 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
